--- a/www/download/COUNTRY.MEX.zdW16.xlsx
+++ b/www/download/COUNTRY.MEX.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>México</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>9.45304620797337</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>9.33715504647754</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>9.63706782238553</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>10.780741200744</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>11.282543039666</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>10.8937563812771</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>10.8944329024199</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>10.9272419594062</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>11.031427427225</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>13.4917261232782</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>12.6321320584262</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>12.3780604313052</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>13.1601110056932</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>12.7656368539897</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.2816764246078</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>31.748</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>31.448</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>31.609</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>33.468</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>34.829</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>35.203</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>36.683</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>37.417</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>37.982</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>36.633</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>37.267</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>37.792</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>38.861</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>38.612</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>38.997</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>21.181</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20.864</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>20.909</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>22.341</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>23.175</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>23.507</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>24.43</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>24.911</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>25.334</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>24.363</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>24.702</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>25.135</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>25.699</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>25.686</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>67764.535</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>66516.442</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>66853.296</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>70413.953</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>73379.424</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>73758.407</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>76765.912</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>78827.94</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>80011.524</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>77833.22</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>79252.704</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>80303.237</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>82882.043</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>82579.654</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>83500.643</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>45028.956</t>
+          <t>69693746831.7497</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>44016.188</t>
+          <t>68326328345.0979</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>44192.875</t>
+          <t>67768909413.1932</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>47127.747</t>
+          <t>68453445158.5328</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>49012.635</t>
+          <t>71561964133.3476</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>49276.815</t>
+          <t>71489743842.6525</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>51115.588</t>
+          <t>74799000757.8533</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>52515.988</t>
+          <t>75908236162.6948</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>53341.374</t>
+          <t>75759047140.2054</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>51630.229</t>
+          <t>72037324467.9419</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>52437.734</t>
+          <t>74402496584.4899</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>53275.677</t>
+          <t>75324892514.0301</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>54650.62</t>
+          <t>77441712046.0832</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>54220.142</t>
+          <t>77381249441.4538</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>54796.975</t>
+          <t>77703193653.9907</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10004420369.4901</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10637505762.8771</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>11097322500.5604</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>10902825150.9171</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>10623401262.0544</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>10620577891.0359</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>10718925443.4486</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>10800918578.9417</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10384500900.0405</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>10136058858.2956</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>10107450535.0638</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>10035313889.2292</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>10292694430.6513</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>10538139676.7632</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>10547372504.6083</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2809792.94410507</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2615339.90314743</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2575456.43110867</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2711312.5049798</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2632020.8045134</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2374508.93993191</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2237630.14031487</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2103581.16877015</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1988789.69185835</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2345704.3933</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2093708.93252017</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1944005.94436108</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1961224.35117893</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1846627.46909574</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1860937.26405737</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>397521.39490987</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>379492.799808828</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>377543.2130058</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>422319.204726435</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>491279.060713646</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>527590.700927729</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>585444.792222928</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>670338.396258121</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>742201.60113159</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>644375.655564617</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>724729.172427482</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>777152.902556674</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>780556.536839848</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>765601.015817773</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>776303.796438713</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>632215.658695072</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>610735.615911808</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>610208.871906338</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>671045.127346358</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>773086.862652908</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>834155.573647356</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>922264.920360569</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1049909.56686336</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1142845.84642387</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>993132.782807392</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1133264.79425449</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1223292.80769507</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1228511.34074201</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1220434.40437976</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1229790.32095316</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3.50090603322931</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3.13782976772696</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.9823006853922</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3.32252616616859</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>3.61364809546145</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3.6397489388587</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>3.7687231588351</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3.86217793571643</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>4.13663338406492</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>4.09371834968624</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>4.18802776408236</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>4.30882019118309</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>4.30965145892726</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>4.1451341188385</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>4.19531996959987</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.45304620797337</t>
+          <t>472.332812446196</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9.33715504647754</t>
+          <t>509.861972009257</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.63706782238553</t>
+          <t>530.736178151551</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>10.780741200744</t>
+          <t>488.020681653453</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11.282543039666</t>
+          <t>458.404433192198</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10.8937563812771</t>
+          <t>451.811516322691</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>10.8944329024199</t>
+          <t>438.762487296249</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>10.9272419594062</t>
+          <t>433.58028898646</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>11.031427427225</t>
+          <t>409.901036412269</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>13.4917261232782</t>
+          <t>416.035278170489</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>12.6321320584262</t>
+          <t>409.177760808177</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>12.3780604313052</t>
+          <t>399.252424282731</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>13.1601110056932</t>
+          <t>400.503250237029</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>12.7656368539897</t>
+          <t>414.066217291322</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>13.2816764246078</t>
+          <t>410.630452753949</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>317898746.110392</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>1532200675.6073</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>3035171677.15678</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>1978587700.89652</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>1880745222.05065</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>2483015334.18818</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>3036504976.46263</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>2614210949.6013</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>2080111161.37965</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>-283343203.423557</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>1038066389.20677</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>2493024468.98818</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>2056033600.34189</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>1899732765.30311</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1018573133.11384</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>398023131.96606</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>1656441017.60749</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>3264198673.83916</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>2727335787.95607</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2719488105.36302</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>3174008353.01742</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>3694364932.90718</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>3232798343.97883</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>2790766860.76793</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>757092265.668028</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>1911215986.75034</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>3446492357.68796</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>3136463377.66506</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>2856870710.9313</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>2151580201.1082</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>-80124385.8556675</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.879</t>
+          <t>-124240342.000188</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.942</t>
+          <t>-229026996.682381</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.906</t>
+          <t>-748748087.059557</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-838742883.312375</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-690993018.829238</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.433</t>
+          <t>-657859956.444548</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.591</t>
+          <t>-618587394.377537</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.827</t>
+          <t>-710655699.388281</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.505</t>
+          <t>-1040435469.09159</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2.806</t>
+          <t>-873149597.543567</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>3.079</t>
+          <t>-953467888.699783</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>3.118</t>
+          <t>-1080429777.32317</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-957137945.628183</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3.293</t>
+          <t>-1133007067.99435</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>2125.92560523125</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.145</t>
+          <t>2109.72204521187</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>2113.55104601536</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.164</t>
+          <t>2109.48216607848</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>2114.91674014827</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>2096.29200342235</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>2092.33683439771</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.734</t>
+          <t>2108.14451447152</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>2105.51134779807</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>2119.16653053384</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.741</t>
+          <t>2122.82558351787</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2119.55933141096</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2126.53266692615</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2.104</t>
+          <t>2130.42622204398</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2133.35659131843</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>2134.4360084264</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>2115.11644494058</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>2115.01916672867</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>2103.93848958845</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>2106.85375995987</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>2095.2013036211</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>2092.66447676272</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>2106.72921135487</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>2106.56300444543</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>2124.66567813711</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>2126.59943769054</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>2124.84654289207</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.149</t>
+          <t>2132.8081221417</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2138.69696015555</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.228</t>
+          <t>2141.219850014</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>170881.081360836</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>162555.538919027</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>165015.376471482</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>168195.832110599</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>191269.551559849</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>218390.726281824</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>254350.173110254</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>276555.630849681</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>295083.774930813</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>231121.792654395</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>294695.689895568</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>342497.966625352</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>352024.918236554</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>362137.798411377</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>368185.257722264</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>9927632209.3186</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9223183525.824</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>9225449517.98864</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>10165718210.7409</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>11127033856.4476</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>11469666583.2911</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>12538346215.9217</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>12346880119.3396</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>12103608312.4347</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>11855664581.14</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>12890942026.0623</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>13650015740.0763</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>13783557275.1575</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>14291468746.0662</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>14975201191.5562</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>169542.528076759</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>163625.916798272</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>163864.386729149</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>166116.096556827</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>191929.527433748</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>216113.292865955</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>248107.2120951</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>271147.808433412</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>296266.259163886</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>228022.134691346</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>287056.631128684</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>334098.226441282</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>341552.159745685</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>351267.448786752</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>361452.261312641</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>67764.535</t>
+          <t>10062477248.6152</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>66516.442</t>
+          <t>10907732021.3403</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>66853.296</t>
+          <t>12095766617.6853</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>70413.953</t>
+          <t>11863521299.5137</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>73379.424</t>
+          <t>13088971843.4791</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>73758.407</t>
+          <t>13698567791.1239</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>76765.912</t>
+          <t>14942664983.0916</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>78827.94</t>
+          <t>14491522070.636</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>80011.524</t>
+          <t>14273362185.3016</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>77833.22</t>
+          <t>11308380198.7521</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>79252.704</t>
+          <t>13349146532.5397</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>80303.237</t>
+          <t>15539428373.112</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>82882.043</t>
+          <t>15081996850.5681</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>82579.654</t>
+          <t>15397005552.6301</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>83500.643</t>
+          <t>15506580970.5114</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45028.956</t>
+          <t>1338.55328407737</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>44016.188</t>
+          <t>-1070.37787924491</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>44192.875</t>
+          <t>1150.98974233209</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>47127.747</t>
+          <t>2079.73555377151</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>49012.635</t>
+          <t>-659.975873898799</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>49276.815</t>
+          <t>2277.43341586881</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>51115.588</t>
+          <t>6242.96101515355</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>52515.988</t>
+          <t>5407.82241626885</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>53341.374</t>
+          <t>-1182.48423307253</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>51630.229</t>
+          <t>3099.65796304968</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>52437.734</t>
+          <t>7639.05876688435</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>53275.677</t>
+          <t>8399.74018407046</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>54650.62</t>
+          <t>10472.7584908691</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>54220.142</t>
+          <t>10870.3496246244</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>54796.975</t>
+          <t>6732.99640962344</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>76063.501</t>
+          <t>-134845039.296592</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>74978.157</t>
+          <t>-1684548495.51631</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>74644.033</t>
+          <t>-2870317099.69662</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>75030.433</t>
+          <t>-1697803088.77285</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>77985.678</t>
+          <t>-1961937987.03151</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>77965.015</t>
+          <t>-2228901207.83285</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>81550.897</t>
+          <t>-2404318767.16989</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>82531.618</t>
+          <t>-2144641951.29633</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>82522.877</t>
+          <t>-2169753872.86683</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>78665.003</t>
+          <t>547284382.387866</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>81012.14</t>
+          <t>-458204506.477447</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>82200.415</t>
+          <t>-1889412633.03572</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>84224.075</t>
+          <t>-1298439575.41062</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>84195.039</t>
+          <t>-1105536806.56391</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>77703.194</t>
+          <t>-531379778.955162</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>320070.185190243</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>338794.270284835</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>349094.097738509</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>336539.698662634</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>373281.439937092</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>416335.521184772</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>475820.17295272</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>510858.274730117</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>554552.07749075</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>426550.544619381</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>509534.605570714</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1.192</t>
+          <t>582577.724122347</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>594988.487552545</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>609020.875085791</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>617337.802783074</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>43821.685</t>
+          <t>0.227314905383035</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>42455.932</t>
+          <t>0.219948519674313</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>41929.4</t>
+          <t>0.221043216073954</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>43080.865</t>
+          <t>0.223854260539887</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>45475.995</t>
+          <t>0.236652133660163</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>45216.175</t>
+          <t>0.243192438090457</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>47481.677</t>
+          <t>0.25193387364005</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>48465.322</t>
+          <t>0.256911794704477</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>49200.412</t>
+          <t>0.255302048010514</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>46740.072</t>
+          <t>0.22303411875309</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>47580.813</t>
+          <t>0.239009945174054</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>47853.595</t>
+          <t>0.248694083848665</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>49203.97</t>
+          <t>0.249635404981859</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>48542.685</t>
+          <t>0.24969933942935</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>49050.056</t>
+          <t>0.249918266825772</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>171742.8713083</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>188027.137155134</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>202280.884133982</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>195260.282411858</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>201879.523821809</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>225437.777326331</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>246430.087205737</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>263754.445363993</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>282464.249866712</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>235024.781289102</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>264819.135153495</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>289266.548738037</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>292813.589123655</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>314645.170657391</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>319940.303599964</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>10919.16</t>
+          <t>222557.701398238</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11627.375</t>
+          <t>242996.711723845</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>12162.978</t>
+          <t>260890.203512604</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>11911.637</t>
+          <t>250819.971520876</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>11548.954</t>
+          <t>259967.593334322</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>11569.028</t>
+          <t>288973.009038836</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>11675.046</t>
+          <t>316045.854718983</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>11729.112</t>
+          <t>337437.169451314</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>11306.196</t>
+          <t>360831.526858095</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>11035.66</t>
+          <t>298767.012882749</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>10968.666</t>
+          <t>336592.718104172</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>10930.083</t>
+          <t>366982.102186924</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>11163.307</t>
+          <t>370346.042745876</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>11403.232</t>
+          <t>398158.603851226</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>10547.373</t>
+          <t>404887.611140761</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>312.38</t>
+          <t>1722624.36042529</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>278.56</t>
+          <t>1879112.44835813</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>263.34</t>
+          <t>1942336.83246301</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>295.64</t>
+          <t>1905592.94848892</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>324.39</t>
+          <t>2010008.91075313</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>325.94</t>
+          <t>2219810.17455009</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>337.82</t>
+          <t>2432658.93487484</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>347.74</t>
+          <t>2591383.06842127</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>371.79</t>
+          <t>2826610.31516828</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>367.85</t>
+          <t>2504913.57377432</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>378.07</t>
+          <t>2805901.24956789</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>387.42</t>
+          <t>3079158.84245708</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>389.56</t>
+          <t>3117956.34962214</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>375.48</t>
+          <t>3250163.91711135</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>419.53</t>
+          <t>3292534.20970022</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.188</t>
+          <t>415498.420524641</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.007</t>
+          <t>414576.731733956</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.985</t>
+          <t>420566.574226354</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.115</t>
+          <t>421632.949390184</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.005</t>
+          <t>422557.054950369</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>435511.889974158</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.563</t>
+          <t>443818.363100618</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.399</t>
+          <t>453244.388680234</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.282</t>
+          <t>457176.146806905</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.705</t>
+          <t>445594.635809877</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2.398</t>
+          <t>449789.763038717</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2.231</t>
+          <t>457107.077631074</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2.238</t>
+          <t>469388.655435303</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2.117</t>
+          <t>478677.880520519</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.861</t>
+          <t>486185.12905664</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>326022.496240717</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>324403.48359195</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>328958.530529922</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>330710.395584826</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>330965.224029292</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>342242.552595773</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>347507.789857105</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>355126.520319096</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>358713.884617218</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>351208.815289987</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>353878.529276816</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>359992.180689271</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>369854.68391099</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>376073.39279719</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>381540.74420626</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>391578.193500585</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>413308.001317944</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>429340.380146521</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>426575.100374011</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>475672.897405668</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>539841.04844684</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>612869.188708097</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>665756.874874903</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>721639.402390106</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>558681.19147941</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>670638.303823031</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>765768.587349379</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>778352.296053683</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>811563.783139814</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>822864.443152842</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>45028956000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>44016188000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>44192875000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>47127747000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>49012635000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>49276815000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>51115588000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>52515988000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>53341374000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>51630229000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>52437734000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>53275677000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>54650620000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>54220142000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>54796975000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>67764535433.6991</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>66516442119.8142</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>66853296093.0024</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>70413952732.8604</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>73379424202.5116</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>73758406520.8177</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>76765912043.6864</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>78827939848.0456</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>80011524485.7955</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>77833219858.3709</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>79252704288.2223</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>80303237474.0902</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>82882043350.6905</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>82579653610.9187</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>83500643021.8915</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>43821685015.263</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>42455931779.2968</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>41929399882.0835</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>43080864970.2255</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>45475995286.7534</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>45216174601.7824</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>47481677433.9022</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>48465322060.1672</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>49200411642.2272</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>46740072407.9748</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>47580812577.6006</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>47853595217.6054</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>49203969517.3913</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>48542685264.3783</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>49050056095.9473</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>31748216</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>31448123</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>31608837</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>33467686</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>34828912</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>35203494</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>36683335</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>37417215</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>37982023</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>36633161</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>37267340</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>37792488</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>38860525</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>38612134</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>38996763</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>21180871</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20863501</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>20909301</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>22340908</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>23174735</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>23506656</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>24429904</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>24911000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>25334166</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>24363460</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>24701857</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>25135261</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>25699403</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>25450373</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>25685802</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>67764535433.6991</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>66516442119.8142</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>66853296093.0024</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>70413952732.8604</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>73379424202.5116</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>73758406520.8177</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>76765912043.6864</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>78827939848.0456</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>80011524485.7955</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>77833219858.3709</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>79252704288.2223</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>80303237474.0902</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>82882043350.6905</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>82579653610.9187</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>83500643021.8915</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>45028956000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>44016188000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>44192875000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>47127747000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>49012635000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>49276815000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>51115588000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>52515988000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>53341374000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>51630229000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>52437734000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>53275677000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>54650620000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>54220142000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>54796975000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1093021.60297776</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1144825.36889574</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1187559.05305344</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1163601.03658961</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1264788.82493296</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1435254.98091125</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1601970.15663729</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1734393.61109023</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1874876.70507398</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1473112.9152775</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1741137.42896123</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1960922.18806455</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2000442.35376764</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2104457.9027096</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2130489.33858109</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>614135.895427753</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>656304.713577284</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>690230.575772909</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>677395.067442502</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>735640.484092552</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>828814.061341095</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>928915.04260097</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1003194.04588196</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1082470.9259848</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>857448.20569631</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1007231.02010645</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1132750.68759739</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1148698.33492421</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1209722.3909078</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1227752.05128193</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2764788.46281861</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2875710.0860133</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>3011204.73284858</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3312361.15335407</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>3307970.28497678</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>3327644.53663205</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3423698.50633412</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3436559.95306035</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3542458.0837068</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>3756860.71862258</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>3749533.45913402</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>3838820.29811897</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>3974402.39012611</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>3926420.43916442</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>4017172.00049154</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
